--- a/results/Int All Data 0.1/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.1/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0007849053221002267</v>
+        <v>-0.002332540252447011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005586087791840344</v>
+        <v>0.0003234661513892811</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000748342073237518</v>
+        <v>0.0005445137723303983</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0004792254960500486</v>
+        <v>0.0003122299305551746</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.727613217173857e-05</v>
+        <v>-0.0004388818565615782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002968477003969305</v>
+        <v>-0.0007615533372246486</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.000220185918331115</v>
+        <v>-0.00176661503887481</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.890813354785363e-05</v>
+        <v>-0.0005183231079015449</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008577952083831898</v>
+        <v>0.000438182663419816</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.066011434165076e-05</v>
+        <v>0.0002316102454870728</v>
       </c>
       <c r="L3" t="n">
-        <v>3.062094411266925e-05</v>
+        <v>0.0004078203623889175</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002538432462356766</v>
+        <v>-0.001166691915257067</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.002272182618054664</v>
+        <v>-0.001276040617302184</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.238003795260744e-05</v>
+        <v>-0.0001928889453751238</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000127841759743238</v>
+        <v>-5.415618485598461e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001129340321736442</v>
+        <v>0.003879849109691438</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0005438615473050201</v>
+        <v>-0.0003885980462568373</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001640800424648403</v>
+        <v>-0.0003382049985076618</v>
       </c>
       <c r="T3" t="n">
-        <v>4.344567823167166e-05</v>
+        <v>0.0002348552580489427</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003842467461742049</v>
+        <v>-0.0002779451540378064</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.001018504464430043</v>
+        <v>-0.0005272588692766811</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.001295395881570892</v>
+        <v>-0.001145761166873194</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0009306630843172672</v>
+        <v>-0.003151702223622185</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004262410554778683</v>
+        <v>0.0002812763037705246</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004785732819530363</v>
+        <v>0.001166533318288043</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008095373888954459</v>
+        <v>0.0009332984806566979</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001433031142675966</v>
+        <v>1.596150570694287e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0004662708324503861</v>
+        <v>-0.0003640116212052302</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002993940863330604</v>
+        <v>0.001350139837967504</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0009999808177808809</v>
+        <v>-0.0002006026822392738</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0004573296979677131</v>
+        <v>-0.0009383018126177311</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.510243533276005e-05</v>
+        <v>0.0001539903963728561</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0002653268084884918</v>
+        <v>0.0004110777652326358</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0003399193288096003</v>
+        <v>-0.0001822234773037102</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0005224175945582821</v>
+        <v>-0.002245846140278825</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.003254883960581237</v>
+        <v>0.004212725792415536</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0003396703000035372</v>
+        <v>-0.0006870751009365972</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.00254245594124046</v>
+        <v>0.00284107449629843</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0008603658251534717</v>
+        <v>0.001220308501867138</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0009344004501852977</v>
+        <v>-0.001060459079616652</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0002063403059875669</v>
+        <v>0.0001741504937359939</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001623530217886313</v>
+        <v>0.001444998491698102</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.001900725304876191</v>
+        <v>0.002760247196275838</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005012549490480422</v>
+        <v>-0.0004182380363711369</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001265535479549075</v>
+        <v>-0.001228448477348894</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0004079206949811587</v>
+        <v>0.000370349755017615</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.761637503949429e-05</v>
+        <v>0.0003567749898017547</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.00126638431203179</v>
+        <v>-0.0008205683955511188</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001548336441961884</v>
+        <v>-0.000371198631751869</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0002795185501205977</v>
+        <v>0.001008663126620716</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.002347005414783726</v>
+        <v>0.0004270137846391097</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.003170625595980551</v>
+        <v>0.00320932846033337</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.00605672923941448</v>
+        <v>0.005448686556307374</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002520282508583004</v>
+        <v>-0.0001099040414141362</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0004301188190929483</v>
+        <v>-8.231988658691236e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0004297164416664012</v>
+        <v>-7.005005282506539e-06</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.003683374287365373</v>
+        <v>0.001491216795160726</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0006258371094685722</v>
+        <v>0.0004683195499087658</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.0004578333899207731</v>
+        <v>-0.0004521791460954871</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003081002049035253</v>
+        <v>0.004456997032870991</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001039573616941895</v>
+        <v>0.0008425752509694252</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0004145308251912882</v>
+        <v>-0.00076203310697744</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0001537690361676214</v>
+        <v>8.83419057699597e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.002365759838250734</v>
+        <v>-0.0002850795888061874</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.002681966371410942</v>
+        <v>0.002528299855148707</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.085378350719869e-05</v>
+        <v>-0.0007640092240581984</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.000371061805616798</v>
+        <v>-0.0003947527855394284</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0008494906167584027</v>
+        <v>-0.0006426208614521588</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0004410380681222692</v>
+        <v>-0.0001403087825004323</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0006110650804130445</v>
+        <v>-0.0002858844629037827</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0003890812641857344</v>
+        <v>-0.0002888106546598346</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0004380052886486362</v>
+        <v>-0.0009092793628175954</v>
       </c>
       <c r="BW3" t="n">
-        <v>-3.511617978898763e-05</v>
+        <v>-2.154638539999532e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0008335954808123978</v>
+        <v>0.0002730576107095817</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.137022802927047e-05</v>
+        <v>0.0005238939077157955</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0004473095219590173</v>
+        <v>-0.002083804254915624</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0002998812583951005</v>
+        <v>-7.919373350353977e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001514261520056881</v>
+        <v>0.0006406929441300903</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.000214065408912476</v>
+        <v>0.0001244309465968706</v>
       </c>
       <c r="CD3" t="n">
-        <v>8.313341727791298e-05</v>
+        <v>-0.001402395777097999</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0002463445104401818</v>
+        <v>-0.0004973656352263655</v>
       </c>
       <c r="CF3" t="n">
-        <v>-2.359991488349532e-05</v>
+        <v>-8.585042669540866e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.000882819014355014</v>
+        <v>-0.0008568060395578338</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0001987362837608064</v>
+        <v>0.001100656796144512</v>
       </c>
       <c r="CI3" t="n">
-        <v>-3.436633322267958e-05</v>
+        <v>-0.0005536493064609916</v>
       </c>
       <c r="CJ3" t="n">
-        <v>7.179859208342743e-06</v>
+        <v>-5.240414778906456e-07</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0002766869645760073</v>
+        <v>-0.0004654346588667681</v>
       </c>
       <c r="CL3" t="n">
-        <v>-7.420018282254686e-05</v>
+        <v>0.0009208649445585658</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.0001694190242769044</v>
+        <v>-0.0005785575408805344</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0007496707691940285</v>
+        <v>-0.0008199507264236925</v>
       </c>
       <c r="CO3" t="n">
-        <v>7.484575496386813e-05</v>
+        <v>-0.000342147279658045</v>
       </c>
       <c r="CP3" t="n">
-        <v>-3.693165266506315e-05</v>
+        <v>9.434050429053533e-06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0004958445283847013</v>
+        <v>0.0003093412111678117</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0008211645302220929</v>
+        <v>-0.0007132861758446984</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0005076999745472833</v>
+        <v>-0.001687717217163797</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.00112444990826426</v>
+        <v>-0.002537116943368061</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0.0001284741351320906</v>
+        <v>4.454027083817147e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>7.062741307052754e-05</v>
+        <v>2.577377693994021e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.0003897287069175959</v>
+        <v>-0.0009711873911202028</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.0009664776294524101</v>
+        <v>-0.0021070051937534</v>
       </c>
       <c r="CZ3" t="n">
-        <v>6.892630993149406e-06</v>
+        <v>0.0001754053548846435</v>
       </c>
       <c r="DA3" t="n">
-        <v>9.342618793518164e-05</v>
+        <v>-0.000222965213907339</v>
       </c>
       <c r="DB3" t="n">
-        <v>-8.353745128403257e-06</v>
+        <v>-0.0005026849429577018</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0004559551306171496</v>
+        <v>-0.0009732168277251506</v>
       </c>
       <c r="DD3" t="n">
-        <v>-8.151056685656299e-05</v>
+        <v>-4.77265051331377e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0002207700481753305</v>
+        <v>-0.00123321664779762</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0005180760555880293</v>
+        <v>-0.001586290862661319</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0002656175443253439</v>
+        <v>-0.0006917459059123654</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.0001225203833174438</v>
+        <v>-0.002019872960842616</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.0006299224460714736</v>
+        <v>-0.0008375486854082983</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0003641200711585357</v>
+        <v>-0.001566166286960801</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.001083722668564941</v>
+        <v>-0.001346034315050207</v>
       </c>
       <c r="DL3" t="n">
-        <v>3.441426052623543e-05</v>
+        <v>0.0002217971416288822</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0002660828819674032</v>
+        <v>-0.0003889923304414611</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0009678592687504619</v>
+        <v>-0.003522537326618025</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0009930196876800081</v>
+        <v>-0.001986613728020143</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.002024260737590235</v>
+        <v>-0.002502853139203847</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.292961886240954e-05</v>
+        <v>7.047070344996297e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.0001632517825884417</v>
+        <v>5.319435151233565e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.000276358080799971</v>
+        <v>-7.964688488445559e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.002607310331429569</v>
+        <v>-0.002937486311886626</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001729464399958212</v>
+        <v>-0.002480276083701238</v>
       </c>
       <c r="DV3" t="n">
-        <v>7.724990343762617e-06</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>7.825944291424138e-06</v>
+        <v>-2.672492533700737e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0002495543308300619</v>
+        <v>6.445308674438676e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001803999130901378</v>
+        <v>-0.002067803469754531</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0001388760222425833</v>
+        <v>-0.0001779231913618517</v>
       </c>
       <c r="EA3" t="n">
-        <v>-8.406198114167768e-05</v>
+        <v>-0.001963002228367055</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.001270607244366271</v>
+        <v>-0.003857996485310051</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0002782883405472225</v>
+        <v>-1.923623287245603e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.001251797302177177</v>
+        <v>-0.001932722187428106</v>
       </c>
       <c r="EE3" t="n">
-        <v>5.344461478205886e-05</v>
+        <v>4.941007283521981e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>3.039650544729213e-05</v>
+        <v>-0.0009065272805696678</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0005587644490902045</v>
+        <v>-0.0005954281179417886</v>
       </c>
       <c r="EH3" t="n">
-        <v>5.137478027617103e-05</v>
+        <v>-0.0003080875720977239</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0001395198238678385</v>
+        <v>-0.001754669203176638</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0003389179270363152</v>
+        <v>0.0002542729637639429</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0003538540933645118</v>
+        <v>-0.001076035420301971</v>
       </c>
       <c r="EL3" t="n">
-        <v>1.140398886063321e-05</v>
+        <v>7.964073318161846e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>8.7749387968169e-05</v>
+        <v>0.0001037785483004039</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0002848386121694557</v>
+        <v>5.869341786649663e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0002427552652584408</v>
+        <v>-0.0002104604731032178</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.001092901676293182</v>
+        <v>-0.001704418530949554</v>
       </c>
       <c r="ER3" t="n">
-        <v>-4.046616286370042e-05</v>
+        <v>-2.554912178889923e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-9.844398907019268e-05</v>
+        <v>-0.0001143994878461674</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0003516265022471664</v>
+        <v>-5.235560193717103e-06</v>
       </c>
       <c r="EU3" t="n">
-        <v>-6.215871903705652e-05</v>
+        <v>-0.001053741589995123</v>
       </c>
       <c r="EV3" t="n">
-        <v>-3.019674407232831e-05</v>
+        <v>-0.000213795418141427</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0008226555258319347</v>
+        <v>-0.0002105910189342586</v>
       </c>
       <c r="EX3" t="n">
-        <v>-5.981350146062382e-05</v>
+        <v>-0.0001094570133257011</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0001479964712213355</v>
+        <v>-0.0002552604571603056</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002634559188039788</v>
+        <v>0.004144045543662831</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001240169589268546</v>
+        <v>0.0009748292057216159</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00173346074143675</v>
+        <v>0.001063022797914946</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001088807905326857</v>
+        <v>0.0006634667921147187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000543654912500594</v>
+        <v>0.00116286987264325</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001068574595216242</v>
+        <v>0.002011538922944924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00182701565565019</v>
+        <v>0.00386180385155812</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002170645515897457</v>
+        <v>0.002700294816407086</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002098262286697904</v>
+        <v>0.003249117495696304</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003102457249785535</v>
+        <v>0.0009268182870443905</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002214359886102886</v>
+        <v>0.0009234753630402992</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001093514332788721</v>
+        <v>0.002797693760147379</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005175160103629956</v>
+        <v>0.003900903579975258</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003622450421890004</v>
+        <v>0.002224179211839522</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0006239338338992557</v>
+        <v>0.001090694863336631</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01012497153251008</v>
+        <v>0.008160300369602471</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001811830864164782</v>
+        <v>0.001813577781153891</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002222091853681502</v>
+        <v>0.003546947510615919</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006610140225715924</v>
+        <v>0.001015488233580441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002472877451712187</v>
+        <v>0.002285097826917745</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002243000366579497</v>
+        <v>0.00512921547954698</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004367684904044538</v>
+        <v>0.002436903159687944</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005779883972925189</v>
+        <v>0.009465910596472768</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007340257048918209</v>
+        <v>0.0017547566621266</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004856683162745709</v>
+        <v>0.009265330176957104</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001689243591716494</v>
+        <v>0.008251747470558072</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0004047823553870935</v>
+        <v>0.0008309977591185336</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001842801309689536</v>
+        <v>0.002123882066068736</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.009361689217426618</v>
+        <v>0.008261489900393409</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01040505391437758</v>
+        <v>0.007340544472838392</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003869429768063411</v>
+        <v>0.00762520246852305</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006260796976278862</v>
+        <v>0.002120761446866834</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009007066814863239</v>
+        <v>0.001083494988882956</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001169262839302033</v>
+        <v>0.001378250532399196</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005286304011186602</v>
+        <v>0.0097615140802173</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005454159922134671</v>
+        <v>0.01029294439285194</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007427366085659657</v>
+        <v>0.001648433171312897</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.007578928836549267</v>
+        <v>0.007388629222083915</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003865290350533563</v>
+        <v>0.005514855915345667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00719301483712121</v>
+        <v>0.005957472814523403</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001319137563021672</v>
+        <v>0.001074744507553459</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002399760030267629</v>
+        <v>0.004827685043935008</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005519599799468987</v>
+        <v>0.007949240624102964</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001176454567163295</v>
+        <v>0.00148017333847226</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.002355712572364558</v>
+        <v>0.001241693328025513</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001540553218100531</v>
+        <v>0.003157953155883473</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001512981333125364</v>
+        <v>0.001591771524063353</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003005777991760315</v>
+        <v>0.002366342457167268</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001561212225854681</v>
+        <v>0.0010043050537515</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002248702921996965</v>
+        <v>0.002872219420054709</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.006452906031033651</v>
+        <v>0.004929654620488444</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.009882249673802574</v>
+        <v>0.007973064014883539</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00747307649302533</v>
+        <v>0.009712210587368443</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004877653969246428</v>
+        <v>0.001033446294363872</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0006316825705237306</v>
+        <v>0.0004668200747632274</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004291272886654053</v>
+        <v>0.004141547138516732</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.008233134597601617</v>
+        <v>0.007537286584086677</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.007519567099228945</v>
+        <v>0.007825503324913876</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0006691764221995657</v>
+        <v>0.0008242782341092941</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.01010925982431089</v>
+        <v>0.006523820184981759</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002433196844565233</v>
+        <v>0.00316988571928874</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001427562232042932</v>
+        <v>0.002018140568659891</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006294401811527741</v>
+        <v>0.000609928071020212</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.006264161904561425</v>
+        <v>0.001668443277706019</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.008939448039891051</v>
+        <v>0.007310638165089269</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00244945771239016</v>
+        <v>0.002256654623765236</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0005842314792705012</v>
+        <v>0.001644978151796309</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002571495392133227</v>
+        <v>0.00333628302630721</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001013638040460712</v>
+        <v>0.000818715878525493</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001797634606678907</v>
+        <v>0.001527526050617549</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.001051340809349009</v>
+        <v>0.001684835299554316</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001481775267467683</v>
+        <v>0.00172011843942777</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001238674814935041</v>
+        <v>0.0002169561972258209</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.003607443197717856</v>
+        <v>0.002134267091535941</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003301475424753646</v>
+        <v>0.002463960975825074</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002211649377015974</v>
+        <v>0.006189098761591025</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001353214671912719</v>
+        <v>0.001226012215613332</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001671098530456203</v>
+        <v>0.003204463126104968</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001393773203818364</v>
+        <v>0.003636602001488533</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.003816828972574706</v>
+        <v>0.004270682310989652</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00471174504709979</v>
+        <v>0.001557906532133038</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001522311086402575</v>
+        <v>0.002094533126929069</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00144828599460319</v>
+        <v>0.001893126053094624</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008905798898437921</v>
+        <v>0.001901313212278804</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0008463825082982032</v>
+        <v>0.0006437478919246917</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.914378491483912e-05</v>
+        <v>6.009885279609435e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002064545400773576</v>
+        <v>0.001810541148989064</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.002459485174813776</v>
+        <v>0.002172892683590424</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.00089112388649798</v>
+        <v>0.001377911687578199</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0009993417448871179</v>
+        <v>0.001427186640566968</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001003147052738451</v>
+        <v>0.001267144862267714</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0001615577436595935</v>
+        <v>0.0002852398569868174</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002047094758686361</v>
+        <v>0.001544823135961906</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001768521098588095</v>
+        <v>0.002074851463705774</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002286308438585294</v>
+        <v>0.003201487224543274</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002570799846889662</v>
+        <v>0.002900871517920856</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002882271405613934</v>
+        <v>0.0003158955111000956</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0006721650927657115</v>
+        <v>0.0002876092772676391</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002206456331171069</v>
+        <v>0.001842152123810931</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.003010620159154076</v>
+        <v>0.002946553262094486</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001699816605129652</v>
+        <v>0.0008384894938155212</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0003302514213108408</v>
+        <v>0.0004677775787023494</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001307394624126565</v>
+        <v>0.002180368088156665</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.001656969085042456</v>
+        <v>0.003018214731176376</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0002622194549971799</v>
+        <v>0.0005644647585935439</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001579417053538719</v>
+        <v>0.003427906026066132</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.001565364474260588</v>
+        <v>0.003331771998798208</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0007227323739241833</v>
+        <v>0.0008997306471766865</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.001471725999142513</v>
+        <v>0.003114936891473349</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002544723139984139</v>
+        <v>0.002700482665745898</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002669866013495604</v>
+        <v>0.002458921675647483</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.002629478044009731</v>
+        <v>0.002452278296569241</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.000211172303131686</v>
+        <v>0.000348538886090687</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0008725593171150036</v>
+        <v>0.001472028757785714</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.008087871158630428</v>
+        <v>0.006954772121007247</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004185791452581073</v>
+        <v>0.005990619515601663</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.003877642103619404</v>
+        <v>0.003823785087946896</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003409908319452102</v>
+        <v>0.0003634917776250518</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.00044155980015434</v>
+        <v>0.0003536768361184891</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0008227578103701704</v>
+        <v>0.0002263568369169926</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.006608939864715954</v>
+        <v>0.003018246128402377</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.006017483540684287</v>
+        <v>0.007406939100656047</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.442856438909697e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0003669467658057551</v>
+        <v>0.0002684029292514145</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001733860637807487</v>
+        <v>0.001198543704997497</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.004237104347459401</v>
+        <v>0.005530494877220663</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.000188400425464799</v>
+        <v>0.0003854601368953997</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002404091508974487</v>
+        <v>0.002924562805806798</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003378413321357274</v>
+        <v>0.004650396338368802</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.001173175551753469</v>
+        <v>0.001140130490003842</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.002394279576769869</v>
+        <v>0.003539821554789905</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001763651984349321</v>
+        <v>0.0001759852717553386</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0005648936625298214</v>
+        <v>0.001274332308128045</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001279555173046681</v>
+        <v>0.001072003504825716</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0003742003865413945</v>
+        <v>0.0008206257452112276</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002469369440572853</v>
+        <v>0.001577159602523699</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001055212535055104</v>
+        <v>0.0007292197041299027</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001846309520666927</v>
+        <v>0.001996009240191576</v>
       </c>
       <c r="EL4" t="n">
-        <v>1.836220733643171e-05</v>
+        <v>2.959075142816341e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0001231693425018311</v>
+        <v>0.0003863725016871109</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.000551795631422661</v>
+        <v>0.0001735578085786594</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0004172324224082048</v>
+        <v>0.0007957438661215603</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001708613184508086</v>
+        <v>0.00210901129685995</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.000104020137200769</v>
+        <v>0.0005396544914570713</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0002268550540948423</v>
+        <v>0.0002454187243540836</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0009184197771734516</v>
+        <v>0.0009311895736208362</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001408710806990839</v>
+        <v>0.002586772627086979</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.000544033964819422</v>
+        <v>0.0003973142025587764</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.002182966779820651</v>
+        <v>0.00109959823176696</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001035409375454766</v>
+        <v>0.001232848611771914</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0008279091572737805</v>
+        <v>0.0005172843180597589</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004905368868288918</v>
+        <v>-0.01224410969486292</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0007338740826573709</v>
+        <v>-0.0004381161007666834</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.005330243337195795</v>
+        <v>-0.0003828483920367387</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002526315789473621</v>
+        <v>-0.0007227082540889995</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0008032128514056103</v>
+        <v>-0.003006967363403035</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001467748165314764</v>
+        <v>-0.005175743530320631</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.003862495171881009</v>
+        <v>-0.01135573580533027</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.004336249524534108</v>
+        <v>-0.006049004594180685</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.002548497527577109</v>
+        <v>-0.003859649122807052</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007227082540890994</v>
+        <v>-0.0008800880088008945</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0002190580503833362</v>
+        <v>-0.000843417675100866</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001251422070534758</v>
+        <v>-0.0069524913093859</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01144922023583116</v>
+        <v>-0.009020902090209037</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.005600617999227476</v>
+        <v>-0.002450229709035223</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.001022270901788947</v>
+        <v>-0.001320132013201347</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01599123767798467</v>
+        <v>-0.005111354508944866</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.004298212248003109</v>
+        <v>-0.003866768759571215</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003233168505135109</v>
+        <v>-0.006025492468134453</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00157894736842098</v>
+        <v>-0.001554797117937012</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.004417670682730923</v>
+        <v>-0.004336249524533997</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.004866743916570093</v>
+        <v>-0.008922363847045233</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01286210892236385</v>
+        <v>-0.005321592649310869</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0168018539976825</v>
+        <v>-0.02904596369254542</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7.01754385964426e-05</v>
+        <v>-0.002877192982456189</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.00694736842105258</v>
+        <v>-0.0102105263157895</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001333333333333286</v>
+        <v>-0.0113943607570491</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0008342813803565053</v>
+        <v>-0.001540154015401551</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003322380430814154</v>
+        <v>-0.003347280334727998</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.008762322015334046</v>
+        <v>-0.01943527686101947</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.02483584395519504</v>
+        <v>-0.01328698339127081</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.009694862881421362</v>
+        <v>-0.02139822325222097</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001022270901788969</v>
+        <v>-0.002285714285714313</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001569916027747342</v>
+        <v>-0.002126879354602151</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001293267402054099</v>
+        <v>-0.002701674277016697</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.008845113943607551</v>
+        <v>-0.02568559289300892</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.003385317611259076</v>
+        <v>-0.01114492202358306</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0007368421052631024</v>
+        <v>-0.003369065849923425</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.01175438596491222</v>
+        <v>-0.008245614035087733</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.01100811123986093</v>
+        <v>-0.003508771929824594</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02074159907300114</v>
+        <v>-0.01637697952877563</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.00308771929824555</v>
+        <v>-0.002126879354602163</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.001929824561403482</v>
+        <v>-0.004070407040704094</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.00976263399693722</v>
+        <v>-0.006875241405948263</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.001224489795918304</v>
+        <v>-0.003300330033003329</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.005878057685286586</v>
+        <v>-0.003128621089223671</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.002819621475473133</v>
+        <v>-0.00432709937660436</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.00156012176560123</v>
+        <v>-0.002493582691602514</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.009038238702201596</v>
+        <v>-0.0069524913093859</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.003476245654692922</v>
+        <v>-0.002662609357169998</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004016064257028096</v>
+        <v>-0.002258805513016837</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01814378090528721</v>
+        <v>-0.006566241792197791</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.009565534866739677</v>
+        <v>-0.004363769710304399</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.002815829528158287</v>
+        <v>-0.003520352035203545</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0001901863826550221</v>
+        <v>-0.001714285714285735</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0001158748551564281</v>
+        <v>-0.0008805513016845179</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.006863818912011654</v>
+        <v>-0.005658999634903216</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.00635268346111717</v>
+        <v>-0.007886089813800668</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01039011201235996</v>
+        <v>-0.0116394066184861</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001622247972190016</v>
+        <v>-0.00164624808575804</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.0180722891566265</v>
+        <v>-0.003510204081632695</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.003309243058197109</v>
+        <v>-0.002662609357169998</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.004094244882193876</v>
+        <v>-0.004400440044004428</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0008032128514056103</v>
+        <v>-0.0006206644760861302</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01993047508690614</v>
+        <v>-0.003385317611258998</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.008798831690397935</v>
+        <v>-0.006710671067106743</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.004125593282219786</v>
+        <v>-0.00382456140350883</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.000494484594903044</v>
+        <v>-0.004173047473200598</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.00357794815626139</v>
+        <v>-0.006488991888760176</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.003052631578947307</v>
+        <v>-0.001438596491228095</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.00114111829593011</v>
+        <v>-0.004253758709204303</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001894736842105193</v>
+        <v>-0.002201622247972213</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002162997296253377</v>
+        <v>-0.003862495171881075</v>
       </c>
       <c r="BW5" t="n">
+        <v>-0.0003650967506388936</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.003803727653099997</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.004547121378804597</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.01405948242564702</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0.001826484018264796</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.004040816326530661</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0.005441400304413946</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0.0128621089223639</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.002776721186762998</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.00282361569490287</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.005438596491228099</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.0003673469387755146</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.001722817764165374</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-8.163265306122547e-05</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.004718417047184132</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0.002456912357902474</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.003836734693877597</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.00351487060641178</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.002448979591836764</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0.0004081632653061273</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.003183673469387793</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0.005614035087719338</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.008497489378138323</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.009684210526315828</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0.0003828483920367276</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.0002105263157894721</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.005228070175438615</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.007312404287901975</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.0009824561403509291</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.001210121012101217</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.005948242564696837</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.009087719298245622</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.001087719298245648</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.01008111239860951</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.008385964912280729</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.00292998477929981</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.009508771929824588</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.005022831050228249</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.007343987823439846</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.006450366937041363</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-0.0001901863826549999</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.002771929824561425</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.02203508771929825</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.01761403508771932</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.00919273850907688</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.0003803727653099997</v>
+      </c>
+      <c r="DR5" t="n">
         <v>-0.0003862495171881308</v>
       </c>
-      <c r="BX5" t="n">
-        <v>-0.01070175438596485</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>-0.006618486116394107</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-0.002624572080639109</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>-0.003500761035007627</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>-0.002122448979591751</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>-0.00332174584781767</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>-0.009018264840182644</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>-0.01147161066048664</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>-0.00224419931532911</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>-0.003964912280701704</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>-0.001699497875627654</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>-0.001999999999999913</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>-3.805175038051889e-05</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>-0.005631659056316596</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>-0.002446148229280742</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>-0.002008032128514026</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>-0.0006952491309385689</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>-0.002190580503833472</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>-0.0003828483920367276</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>-0.004344651332603133</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>-0.003719298245613967</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>-0.005832367709540343</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>-0.007338740826573942</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>-0.0005325218714340551</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>-0.001387755102040733</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.005832367709540343</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>-0.007068366164542273</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.0003089996137504936</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>-0.0005306122448979544</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>-0.003030303030303006</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-0.004877192982456102</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>-0.0005111354508944621</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-0.003978370027037459</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>-0.004364619544225545</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.0007301935012778316</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>-0.003122807017543783</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.005087719298245563</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-0.007762557077625587</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-0.007838660578386624</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>-0.0004977029096477458</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>-0.000492984452028844</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>-0.02347368421052626</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>-0.0118947368421052</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>-0.01217543859649118</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>-0.0002679938744257093</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>-0.00094925155166119</v>
-      </c>
       <c r="DS5" t="n">
-        <v>-0.002130087485736109</v>
+        <v>-0.000418569254185619</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.02087719298245608</v>
+        <v>-0.008406238113351006</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.01859649122807011</v>
+        <v>-0.01957894736842107</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0008371385083714156</v>
+        <v>-0.0004033736707004354</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.003881278538812804</v>
+        <v>-0.001788432267884277</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01340350877192977</v>
+        <v>-0.01638596491228072</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-3.667033370003958e-05</v>
+        <v>-0.0008111239860950636</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.006202435312024368</v>
+        <v>-0.007153729071537229</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.009859649122806947</v>
+        <v>-0.01336423329470843</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.002182235834609492</v>
+        <v>-0.00185964912280705</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.007039573820395761</v>
+        <v>-0.01158748551564315</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0001100110011001187</v>
+        <v>-7.607455306199996e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.0009857612267250792</v>
+        <v>-0.003298245614035133</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.003767123287671259</v>
+        <v>-0.002473363774733595</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0005705591479650441</v>
+        <v>-0.002283105022831022</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002489795918367266</v>
+        <v>-0.003939745075318702</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002488514548238896</v>
+        <v>-0.001217656012176504</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.00517503805175038</v>
+        <v>-0.005446118192352289</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-3.50877192982435e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0.0003803727653099997</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0002662609357170109</v>
+        <v>-0.0001466813348001583</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0001148545176110183</v>
+        <v>-0.001755102040816348</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.005251141552511418</v>
+        <v>-0.005757242390905792</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0003285870755750042</v>
+        <v>-0.001283461679501285</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0007301935012778316</v>
+        <v>-0.0007987828071509995</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.002207001522069996</v>
+        <v>-0.001980198019801993</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002182235834609469</v>
+        <v>-0.007762557077625532</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.00140737923164711</v>
+        <v>-0.0008800880088008945</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.0060882800608828</v>
+        <v>-0.002000000000000024</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.001543859649122747</v>
+        <v>-0.001560121765601175</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001484018264840215</v>
+        <v>-0.0009795918367347055</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002704877042901757</v>
+        <v>-0.003730065464154847</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0001728192983678184</v>
+        <v>-0.0002831827983873492</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000451857938830294</v>
+        <v>-0.0001487271534171192</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0009767865681058862</v>
+        <v>9.520182787509101e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0004013733458789414</v>
+        <v>-0.0004875746838333139</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001035615611432506</v>
+        <v>-0.001255631774847066</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001247020776893323</v>
+        <v>-0.002465911471187959</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0008844646534950928</v>
+        <v>-0.001520699438364911</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0002249133553638927</v>
+        <v>-0.0008866300079725276</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0001748331624148836</v>
+        <v>-0.0001889033016957503</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0001101719015438984</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0002771430989253087</v>
+        <v>-0.0008534805961561891</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.00694307413197458</v>
+        <v>-0.002894632195502661</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0008624152743509028</v>
+        <v>-0.001982279830062003</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0002101279201703693</v>
+        <v>-0.0006841474148195969</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001478124126362868</v>
+        <v>-0.002554958825635553</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.000599358539647446</v>
+        <v>-0.0004669850690834282</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0005822250879879449</v>
+        <v>-0.002978972932160704</v>
       </c>
       <c r="T6" t="n">
-        <v>-9.513661287606223e-05</v>
+        <v>-0.0002008205892018999</v>
       </c>
       <c r="U6" t="n">
-        <v>-6.656885239165466e-05</v>
+        <v>-0.001876437866677827</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.002133551608634182</v>
+        <v>-0.00319782831525475</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001535931879909033</v>
+        <v>-0.003063510351384199</v>
       </c>
       <c r="X6" t="n">
-        <v>1.896094046266173e-05</v>
+        <v>-0.001873626232748502</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.167583425004345e-06</v>
+        <v>-0.0001320029718371973</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001620198791455185</v>
+        <v>-0.002856744382285869</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.000332949950982625</v>
+        <v>-0.002096346476752961</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.656237929711598e-06</v>
+        <v>-0.0003826442839830996</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0001625976459552203</v>
+        <v>-0.001599052599323833</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0009092409240924442</v>
+        <v>0.0009520613875067307</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.0005326955245577248</v>
+        <v>-0.001871244816789397</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001231154369943083</v>
+        <v>3.421827286325397e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0002472640247610375</v>
+        <v>-0.001285263013444224</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0001261559603059737</v>
+        <v>-2.473737943633758e-05</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0005112327665712818</v>
+        <v>-0.00100481582977355</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.003455478582631726</v>
+        <v>-0.005374672082592865</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0007134703196347153</v>
+        <v>-0.003018340011328083</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.000120397283056406</v>
+        <v>-0.001686894630885693</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.002560050964525948</v>
+        <v>-0.001587733341623032</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.00151612190388341</v>
+        <v>-0.001037023790896433</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1.5733233932827e-05</v>
+        <v>-0.001804728665637667</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0009539897713681995</v>
+        <v>-0.000203308299618915</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0003135703436449977</v>
+        <v>-0.002792582117073475</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0007273993210140578</v>
+        <v>-0.0001679577095024448</v>
       </c>
       <c r="AS6" t="n">
-        <v>-5.715368768934304e-05</v>
+        <v>-0.001004760194000337</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.003059645057022595</v>
+        <v>-0.002352577156547547</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.000285576502855786</v>
+        <v>-0.0001817947140116516</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0009814102177028107</v>
+        <v>-0.0004476117941464519</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001569178776936631</v>
+        <v>-0.001273011295361659</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001147760954898269</v>
+        <v>-0.0006453592727694079</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002095998878289074</v>
+        <v>-9.509680978986856e-05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.004023211567732074</v>
+        <v>-0.001233044991246113</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.001461538847948751</v>
+        <v>-0.0008181108987573293</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0007221490498333094</v>
+        <v>-0.001434282937198858</v>
       </c>
       <c r="BC6" t="n">
-        <v>-2.871362940275457e-05</v>
+        <v>-0.0003480468528780672</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0001012891884955763</v>
+        <v>-0.0002454350161117225</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0003276090188163661</v>
+        <v>-0.003802573697042927</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001259695033430297</v>
+        <v>-0.001263443248714671</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001740880408729426</v>
+        <v>-0.003308985186420646</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0009656400485339472</v>
+        <v>-0.001189188884758793</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.00147109620103745</v>
+        <v>-0.0001242786394680562</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0002133575132256898</v>
+        <v>-0.001052771603691005</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0005136660639756014</v>
+        <v>-0.001609752553814508</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0003325953784348829</v>
+        <v>-0.0003342948387003747</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001005983421364695</v>
+        <v>-0.0009618104885083856</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0005499611394586156</v>
+        <v>-0.001575118344927926</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001483518917031904</v>
+        <v>-0.002446872344960186</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0001204301317503598</v>
+        <v>-0.0007803708942322934</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0002755102040816026</v>
+        <v>-0.002024509679883663</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.000596697424844525</v>
+        <v>-0.0006744807329125024</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0003457652502402764</v>
+        <v>-0.0004687356875043542</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001405853808708044</v>
+        <v>-0.001444673563834187</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001858434599240635</v>
+        <v>-0.002445318502484628</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-8.84278386523718e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0004811125815513934</v>
+        <v>-0.000843765144763589</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.636329161926746e-05</v>
+        <v>-0.0007891648514706557</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001436721648982617</v>
+        <v>-0.003567870052311378</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0006790607705198875</v>
+        <v>-0.00100930912294048</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003576323387957297</v>
+        <v>-0.0008121009999645462</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0006562733840169116</v>
+        <v>-0.001727810419726869</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0008595049654685633</v>
+        <v>-0.001449263076992596</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0001737740080188177</v>
+        <v>-0.00152117621400695</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001029470692386553</v>
+        <v>-0.00140706366134396</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001516367672972632</v>
+        <v>-0.001254763793336988</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0001712676308201294</v>
+        <v>-0.0002378306850705891</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0003633965190940586</v>
+        <v>-0.0009729422048749131</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-2.750275027502968e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0004614141732717375</v>
+        <v>-0.001128753227216406</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001475553622948722</v>
+        <v>-0.0002464525134581952</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.000318225950676454</v>
+        <v>-0.001254797392001594</v>
       </c>
       <c r="CN6" t="n">
-        <v>9.480470231323923e-06</v>
+        <v>-0.001015442841212422</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.000275712853439733</v>
+        <v>-0.001365506268199346</v>
       </c>
       <c r="CP6" t="n">
-        <v>-2.85605483625273e-05</v>
+        <v>-0.0001605422203198759</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0001333109957870421</v>
+        <v>-8.096847682913244e-05</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002069305049511563</v>
+        <v>-0.001471788019958892</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.0003826921273869327</v>
+        <v>-0.003269748904715058</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001703084685642539</v>
+        <v>-0.003147657672570805</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0003083193887202074</v>
+        <v>-0.0001670221556080848</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0.0001195239386952457</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.0005855080163765015</v>
+        <v>-0.0007893350018786909</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0005766511100203902</v>
+        <v>-0.003764857097954727</v>
       </c>
       <c r="CZ6" t="n">
         <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>-0.0004466043691595867</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0003800310296023096</v>
+        <v>-0.001208896574588969</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.0004265953825973806</v>
+        <v>-0.001205415418902245</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0002857203303733763</v>
+        <v>-0.0003821132548582406</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0001849161025317292</v>
+        <v>-0.00178224327273572</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0009556396699511112</v>
+        <v>-0.001881914726814538</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0001547719171596157</v>
+        <v>-0.0008890084794584058</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.00071911615700066</v>
+        <v>-0.002887286445539497</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.002530390683957767</v>
+        <v>-0.002617322401696254</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0002559726962457431</v>
+        <v>-0.002002521387633266</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0007495052774017047</v>
+        <v>-0.00096065303721867</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>9.656237929700495e-06</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0002572792160722204</v>
+        <v>-0.0009767700319520012</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0005744469256934809</v>
+        <v>-0.003745245514788548</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001392084719368358</v>
+        <v>-0.001931386817506583</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.002051048845945524</v>
+        <v>-0.005184425406010887</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0001224489795918382</v>
+        <v>-8.250825082508907e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0001874277961365772</v>
+        <v>-0.0001999465061150396</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0001713963913398203</v>
+        <v>-0.0001793770139634804</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.002295006248981099</v>
+        <v>-0.004869863454622748</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0006042616393896333</v>
+        <v>-0.005207112970711253</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-8.53242320819153e-05</v>
+        <v>-0.0002029184895063207</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.001139067881683634</v>
+        <v>-0.0005452867399435623</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.001164308541763576</v>
+        <v>-0.002092767758753183</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0.0003955875039558965</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0002538543874536448</v>
+        <v>-0.00413508252877349</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001987956300507432</v>
+        <v>-0.006267220168261018</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.001223626546755172</v>
+        <v>-0.0005278895469455147</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.001272166324836005</v>
+        <v>-0.001845208304138074</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-2.750275027502968e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0003651207225985942</v>
+        <v>-0.001757200801876449</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0005822510578703422</v>
+        <v>-0.001356068743286806</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0001158748551564392</v>
+        <v>-0.0004511662058442334</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001178921484268938</v>
+        <v>-0.003048285668509182</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0006550219214830262</v>
+        <v>-1.850954777010139e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0005162395882658738</v>
+        <v>-0.001168344049948716</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-8.561643835614251e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-5.476451259583403e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>9.65623792970327e-06</v>
+        <v>-0.0003951523095042542</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.000882857236719084</v>
+        <v>-0.002708300298835187</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-6.639575898307327e-05</v>
+        <v>-9.527267628584578e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0004999618278096557</v>
+        <v>-0.0005358639675150989</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0009276763336913268</v>
+        <v>-0.000730755460078783</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0.0004563287982918996</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0003279526205581751</v>
+        <v>-0.0004427576891493867</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0003420758486662068</v>
+        <v>-0.001172826487669692</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0005267566515656602</v>
+        <v>-0.0004763126915101057</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0004750274224209705</v>
+        <v>-0.001812257323020522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002232510132074761</v>
+        <v>5.707762557079499e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-9.248308700192666e-05</v>
+        <v>0.0002093280982471357</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001324921607806839</v>
+        <v>0.0003764764270941911</v>
       </c>
       <c r="F7" t="n">
-        <v>-7.724990343762616e-05</v>
+        <v>-9.492971759071378e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002448151910647844</v>
+        <v>-0.0006284332223551903</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003150733977801911</v>
+        <v>-0.0003340857718765189</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0002234959607327947</v>
+        <v>0.0001900065301883358</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000646035605009837</v>
+        <v>-9.561004398236927e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.308623170009578e-05</v>
+        <v>-1.931247585940099e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.931247585940099e-05</v>
+        <v>9.492009791894351e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.53378895011247e-05</v>
+        <v>7.610350076106553e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003081398117430523</v>
+        <v>-0.001845028909486052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002269468730032309</v>
+        <v>-0.0005679545376433059</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001140253816863279</v>
+        <v>-2.352988335270756e-05</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0001905625059749616</v>
+        <v>0.001762022169547223</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.000116229990345984</v>
+        <v>8.163265306121991e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>7.122507122504508e-05</v>
+        <v>0.0003888292158968687</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001370682516464994</v>
+        <v>0.000228484386900224</v>
       </c>
       <c r="U7" t="n">
-        <v>5.848889441534277e-05</v>
+        <v>0.0004176172408524748</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0003725499332152937</v>
+        <v>-0.0001330652859299452</v>
       </c>
       <c r="W7" t="n">
-        <v>-7.729559496412187e-05</v>
+        <v>-0.0005455872117824113</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0004481165319186187</v>
+        <v>-0.0003602578687902702</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001139604469587108</v>
+        <v>0.0001483301024562345</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.862754669419979e-05</v>
+        <v>0.000142111060040212</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0007495729492627779</v>
+        <v>-0.0003100082378724334</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002895384776572752</v>
+        <v>-9.302514687647422e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001228770137287682</v>
+        <v>-0.0004465893359350881</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001174901607657125</v>
+        <v>0.003264715551612002</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002203365556749054</v>
+        <v>0.001184403441742016</v>
       </c>
       <c r="AF7" t="n">
-        <v>5.398837578261541e-05</v>
+        <v>0.0007260800910022902</v>
       </c>
       <c r="AG7" t="n">
-        <v>5.845904225124655e-05</v>
+        <v>0.0001313718416376009</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0003842088420973055</v>
+        <v>0.0005217269948550151</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003538412240647548</v>
+        <v>-0.0002091181116824214</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001144892541772102</v>
+        <v>0.0009893730744260252</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.003170115323070172</v>
+        <v>0.003594460309721148</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0001671179495103148</v>
+        <v>-0.0004028408902036596</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004302865218333929</v>
+        <v>0.001049785945955634</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0002936844704878428</v>
+        <v>-0.0001358554513016863</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0007797018872272799</v>
+        <v>-0.0003812838621745806</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0001329213874213697</v>
+        <v>0.0002854605797777021</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.000939361419551843</v>
+        <v>0.001603102865490319</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.002510800386509643</v>
+        <v>0.001026667287919747</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0001899340782645198</v>
+        <v>-0.0003677594968485742</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.865696773756806e-05</v>
+        <v>-0.0009141727225588647</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0004411632329121728</v>
+        <v>0.0001632653061224509</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.00026624741760079</v>
+        <v>8.931785819832894e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0006788317764272356</v>
+        <v>-0.0001119508513839462</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0001848397775201238</v>
+        <v>-0.0001309567777059983</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001523798973353974</v>
+        <v>0.0001142421934500926</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.0008180410129503489</v>
+        <v>-7.560548651345811e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001697142095552673</v>
+        <v>0.0003224948380897486</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003729110707444483</v>
+        <v>0.002415801605908929</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.862495171881308e-05</v>
+        <v>-0.0001842816775426581</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001238962023944967</v>
+        <v>-7.531075232843908e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.706313518601957e-05</v>
+        <v>0.0006441256370534942</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0007808590966293938</v>
+        <v>-0.0005261392228123941</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0002432935601252183</v>
+        <v>-0.00029050634442499</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.0003907965916742195</v>
+        <v>-0.0002039453250236911</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0033978152201185</v>
+        <v>0.004085762121977315</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001022470559961575</v>
+        <v>0.0002289946570343315</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.836018617976224e-05</v>
+        <v>-0.001205789676973451</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001774544801418698</v>
+        <v>-3.541878647478901e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0004377545236083358</v>
+        <v>-0.0002249583932752264</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001522780044073935</v>
+        <v>0.002455439168785206</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0005151092110622813</v>
+        <v>-0.0009806140293844245</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0003078532110739107</v>
+        <v>-3.823958137477711e-05</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001681453697132851</v>
+        <v>-0.001068164435779895</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0001904802202489176</v>
+        <v>-0.0001898594351814331</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0002278489860012389</v>
+        <v>-9.056320977691712e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0001158748551564281</v>
+        <v>-0.0004375155893445725</v>
       </c>
       <c r="BV7" t="n">
-        <v>-9.127418765971784e-05</v>
+        <v>-0.0002469687766886331</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001136298692892057</v>
+        <v>0.0004177760910772155</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0009046931522637913</v>
+        <v>0.001398769137985406</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0005166136828077816</v>
+        <v>0.000190608385137353</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.083826130052093e-05</v>
+        <v>-0.0002526560721411719</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0002854751197681637</v>
+        <v>-2.665664560103087e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>-9.448002867518682e-05</v>
+        <v>-0.0002603237331098074</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0004189674677627653</v>
+        <v>-0.0001608877486939053</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001016896561450969</v>
+        <v>-0.0004191369607093098</v>
       </c>
       <c r="CF7" t="n">
-        <v>7.236335839066465e-05</v>
+        <v>-0.0002294028731415876</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0004340625763530115</v>
+        <v>-0.0004132866535735636</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0002621601072240965</v>
+        <v>0.0006044848997406038</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0002911772958672509</v>
+        <v>-0.0005699244721336038</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.000153526909120727</v>
+        <v>-0.0001503453517222808</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0006620849252943263</v>
+        <v>0.001062212094934123</v>
       </c>
       <c r="CM7" t="n">
-        <v>-1.418917401945219e-05</v>
+        <v>-3.806624076525544e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0007371328402026644</v>
+        <v>-0.0002472125950404414</v>
       </c>
       <c r="CO7" t="n">
-        <v>3.944128257197811e-05</v>
+        <v>-1.110223024625157e-17</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-3.50877192982435e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0007169176590961668</v>
+        <v>0.0004131467607942363</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0005128108595343017</v>
+        <v>5.67239711632084e-05</v>
       </c>
       <c r="CS7" t="n">
-        <v>-7.942511238700773e-08</v>
+        <v>-0.001083079875863896</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.000931337312873054</v>
+        <v>-0.002521554772086998</v>
       </c>
       <c r="CU7" t="n">
-        <v>-5.476451259583404e-05</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.706430052713208e-05</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-7.616843548864937e-05</v>
+        <v>-0.0004838051139296861</v>
       </c>
       <c r="CY7" t="n">
-        <v>-5.740229920884191e-05</v>
+        <v>-0.002069225229168115</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
       </c>
       <c r="DA7" t="n">
-        <v>7.459221462531308e-05</v>
+        <v>-7.088641647932104e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0002092057459880836</v>
+        <v>0.0002787652834941145</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.0002847387805777757</v>
+        <v>-7.350132603621272e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>-2.248115968059849e-05</v>
+        <v>-1.914241960183638e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0004887652806059017</v>
+        <v>-0.0001799343114227858</v>
       </c>
       <c r="DF7" t="n">
-        <v>-7.590145965346573e-05</v>
+        <v>-0.000257686034239335</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001881359684085315</v>
+        <v>-0.0005669442446252781</v>
       </c>
       <c r="DH7" t="n">
-        <v>9.305725093055605e-05</v>
+        <v>-0.001182745231214782</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0009402137587261883</v>
+        <v>-0.0004503473895270282</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002473292066895672</v>
+        <v>-0.0005090946026189869</v>
       </c>
       <c r="DK7" t="n">
-        <v>-5.869215281119054e-05</v>
+        <v>-0.0004281668595649712</v>
       </c>
       <c r="DL7" t="n">
-        <v>7.611800768103638e-05</v>
+        <v>0.0001073960915431993</v>
       </c>
       <c r="DM7" t="n">
-        <v>2.179768826511274e-05</v>
+        <v>-0.0004489106279830401</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.001024837490722558</v>
+        <v>-0.0005141575772728614</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0002569689724501279</v>
+        <v>-1.873420349455811e-05</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.0003346285962976259</v>
+        <v>-0.002063219506136416</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>2.040816326530637e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>-5.765082690907253e-05</v>
+        <v>0</v>
       </c>
       <c r="DS7" t="n">
-        <v>-1.914241960183638e-05</v>
+        <v>-3.721577799459252e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>-7.655804385433559e-05</v>
+        <v>-0.003268307102819162</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001711242897704579</v>
+        <v>-0.0008954258110854484</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.833516685000314e-05</v>
+        <v>-1.90403655750182e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>-3.927640215362066e-06</v>
+        <v>-1.982589361809727e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0001373859520959975</v>
+        <v>-0.000403694987972697</v>
       </c>
       <c r="DZ7" t="n">
-        <v>9.39369338693985e-05</v>
+        <v>-7.607455306199996e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0001134929229113068</v>
+        <v>-0.0008641476392537318</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0003133874409773141</v>
+        <v>-0.001875516416612299</v>
       </c>
       <c r="EC7" t="n">
-        <v>-7.616843548864937e-05</v>
+        <v>0.0001697922340890279</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0.0002591954303507893</v>
+        <v>-0.000849905258907191</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001732680621658766</v>
+        <v>-0.0007852196948452406</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0003501611170784013</v>
+        <v>-0.0005870527300395167</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0001522939438306392</v>
+        <v>-0.001771947120422901</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0001120831261208488</v>
+        <v>0.0002471276269133848</v>
       </c>
       <c r="EK7" t="n">
-        <v>-5.720052183744162e-05</v>
+        <v>-0.0008533354826576356</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>3.659000438195892e-05</v>
+        <v>5.724577966632061e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>1.90403655750182e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>7.454695159488933e-05</v>
+        <v>-1.770939323740838e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0005227694724965204</v>
+        <v>-0.001092399531132338</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-5.551115123125783e-18</v>
+        <v>-3.659000438196446e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0001534113657376934</v>
+        <v>0.000167824052441029</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0002167666481826813</v>
+        <v>-0.0003742215225706836</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-0.0001985235326538381</v>
       </c>
       <c r="EW7" t="n">
-        <v>-2.824411722807119e-06</v>
+        <v>-0.0001717554195773296</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0002768540800700048</v>
+        <v>2.077573185458312e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0</v>
+        <v>-0.0003301765132586343</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001474834080940224</v>
+        <v>0.0003914347258019008</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009604810354939264</v>
+        <v>0.0001807205181412863</v>
       </c>
       <c r="D8" t="n">
-        <v>5.476451259585902e-05</v>
+        <v>0.0004932729410430991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002466907887953229</v>
+        <v>0.0007091790910724122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001128269823569228</v>
+        <v>0.0002691268288137427</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005711457605191317</v>
+        <v>0.0001534052190643981</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001086781033052078</v>
+        <v>-3.268567701050494e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001122201962587194</v>
+        <v>0.001080827950019009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001595642217282919</v>
+        <v>0.0007227559856832378</v>
       </c>
       <c r="K8" t="n">
-        <v>1.88825748556859e-05</v>
+        <v>7.07446725834282e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>5.742725880552025e-05</v>
+        <v>0.000676963936259456</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001142776227737097</v>
+        <v>0.0002615467239527103</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00143935060696023</v>
+        <v>0.001727777173321748</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001393474983291074</v>
+        <v>0.0008977403764472646</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0005589564342485781</v>
+        <v>0.000160500729972371</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004413991360851225</v>
+        <v>0.009147671221284416</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000430704441041363</v>
+        <v>0.0006260684482730456</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001554745198603888</v>
+        <v>0.003029176875055451</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003914159354254265</v>
+        <v>0.0007158968850697944</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0009517491302794474</v>
+        <v>0.0009140122642704529</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0005997715156130623</v>
+        <v>0.00165413533834585</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001405903642573098</v>
+        <v>0.0007721369302922138</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0008170321080690962</v>
+        <v>0.00074004150573585</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00043804758678819</v>
+        <v>0.0006374610063746261</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002193305726693137</v>
+        <v>0.001350220258596102</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.001641351558004447</v>
+        <v>0.002176871808458192</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0003134117836705447</v>
+        <v>0.0003233421797501579</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001692382752942651</v>
+        <v>0.0001330784509714939</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002969992731622978</v>
+        <v>0.004618701433950156</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.005761095199020183</v>
+        <v>0.004401847143534024</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002263335307889733</v>
+        <v>0.001812040615980767</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002405562907756981</v>
+        <v>0.001122328797884589</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008437074421213137</v>
+        <v>0.00122171266507167</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0009750387513718874</v>
+        <v>0.000951928186015874</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005291764242210372</v>
+        <v>0.003134522951213634</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.006842471514905532</v>
+        <v>0.01221051592338723</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0006787151317871499</v>
+        <v>0.0006439483643286809</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00729433011560536</v>
+        <v>0.006214150994166556</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001141468833152634</v>
+        <v>0.0004759222301374016</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002474774819905415</v>
+        <v>0.002297043960223915</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0008772790151856336</v>
+        <v>0.0005040316279651292</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002948044525034807</v>
+        <v>0.003862716355934886</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.003751150625266595</v>
+        <v>0.003613965360831198</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005991257020438734</v>
+        <v>-1.90403655750182e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0006079297092094372</v>
+        <v>-0.0003341945045261446</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001446687555784823</v>
+        <v>0.000823873661248295</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0009800606306841235</v>
+        <v>0.0009132999462590108</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0006439210473947964</v>
+        <v>0.0006536907222904398</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.000598477982310866</v>
+        <v>0.0002009172734943915</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001597065334404807</v>
+        <v>0.001264769065520946</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001753601632397869</v>
+        <v>0.000554897079630151</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00485613161547904</v>
+        <v>0.003182330009629403</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01118422525141056</v>
+        <v>0.008868732248303184</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000322563259411629</v>
+        <v>0.000229555954181826</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0009966729466469176</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002037593984962452</v>
+        <v>0.001866325461433074</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.006906641774244885</v>
+        <v>0.005192479338052924</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001844276133630438</v>
+        <v>0.002596447550921852</v>
       </c>
       <c r="BH8" t="n">
-        <v>-5.707762557079499e-05</v>
+        <v>3.061224489795955e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.008596914586028046</v>
+        <v>0.006121184811343452</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00212647279432448</v>
+        <v>0.00178227648415569</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0003700957520272635</v>
+        <v>0.0001712437320995019</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0005641400811067232</v>
+        <v>0.0003941619526830725</v>
       </c>
       <c r="BM8" t="n">
-        <v>-1.693435076579875e-05</v>
+        <v>-1.018354102484686e-05</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.004292859500407251</v>
+        <v>0.004840459134150379</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001632176454042586</v>
+        <v>0.001132272253913014</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0006432978188684296</v>
+        <v>0.0006452028208528027</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001956219977676796</v>
+        <v>0.0001523772428739412</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.614697191530572e-05</v>
+        <v>0.0002114647906944433</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0007325432645357566</v>
+        <v>0.0004781522739386784</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004051004415509763</v>
+        <v>0.000194905782685495</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0001194914713313927</v>
+        <v>0.0003248429711424694</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0009050634223399578</v>
+        <v>0.001106813152424163</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002202354938690199</v>
+        <v>0.002439818152687648</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001955062571103539</v>
+        <v>0.001125849971402845</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002324921206160568</v>
+        <v>0.0006809276849835289</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0004701245830145112</v>
+        <v>0.000761114704726551</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0004828062074275136</v>
+        <v>0.0009274792168744384</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001952926915968753</v>
+        <v>0.0002914232169135888</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.002191238890403943</v>
+        <v>1.978861853796088e-05</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.000332888697113326</v>
+        <v>0.0005977023580947983</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0001331465038829305</v>
+        <v>-0.0001234049632319351</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005543726297780299</v>
+        <v>0.001265396514286815</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0004975068393124281</v>
+        <v>-1.642307087853789e-05</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0008206053034577554</v>
+        <v>0.0003823381219026617</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0006166674031540503</v>
+        <v>0.001862782193216056</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0004756914389259653</v>
+        <v>0.0002861497041940164</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001343030251278915</v>
+        <v>0.0001711785997766474</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.000895051921173709</v>
+        <v>0.0005711457605191428</v>
       </c>
       <c r="CP8" t="n">
-        <v>5.500550055004272e-05</v>
+        <v>8.214676889375938e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001395114786203897</v>
+        <v>0.001312362028029523</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.000247575468821884</v>
+        <v>0.0004859721497713159</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0003677953824430119</v>
+        <v>0.0005952460398959442</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0006566849003381864</v>
+        <v>-0.0005661500297578614</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>0.0002284409157459422</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0001414940858909225</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0001464314642771081</v>
+        <v>-0.0001395700806394728</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0008921478338751066</v>
+        <v>0.0005511800021522295</v>
       </c>
       <c r="CZ8" t="n">
-        <v>6.690772903683306e-05</v>
+        <v>2.844141069398009e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0003373297332151526</v>
+        <v>8.568164508758193e-05</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.000618961788031755</v>
+        <v>0.0008383910991655724</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0003285870755750375</v>
+        <v>0.0006136660143509747</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.804101859385123e-05</v>
+        <v>0.0004390281327216777</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001059920354600563</v>
+        <v>0.0004689680265270557</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0001530612244897978</v>
+        <v>0.0001129287968043291</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0004870428250117215</v>
+        <v>-0.0002291131948371799</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0001521640743753799</v>
+        <v>-0.0002089277580947818</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001011601135525419</v>
+        <v>0.0001498337849003467</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0009833512352309809</v>
+        <v>-4.563709382986448e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.000287020470806601</v>
+        <v>-2.852795739826664e-05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0001573194447548914</v>
+        <v>0.0003860745663607001</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0003572947656211078</v>
+        <v>0.0005297325347116883</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.001972944296393248</v>
+        <v>3.598843624312564e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001466924581490978</v>
+        <v>0.0007502546314885812</v>
       </c>
       <c r="DP8" t="n">
-        <v>-0.0001949410101806631</v>
+        <v>0.0005259062689164594</v>
       </c>
       <c r="DQ8" t="n">
-        <v>8.568164508758469e-05</v>
+        <v>7.533246310275909e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.844141069397177e-05</v>
+        <v>0.0002738225629791785</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0003607091478378288</v>
+        <v>-0.0001774150758679788</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001023233722689648</v>
+        <v>0.0008062370952243686</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001799312882438064</v>
+        <v>0.0001447674960395412</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0006877660121222373</v>
+        <v>9.935553168635425e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.000173492655544269</v>
+        <v>0.0007515727863619037</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001605476611575729</v>
+        <v>0.0001095290251916681</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0007245896470682244</v>
+        <v>-0.0001812406620565393</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001041291787122481</v>
+        <v>-0.0001822938704126892</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0001722258252434661</v>
+        <v>0.0006322235378793423</v>
       </c>
       <c r="ED8" t="n">
-        <v>-4.681538589447476e-05</v>
+        <v>-0.0001618939104892525</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0004845928566326235</v>
+        <v>3.173394262502016e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0001916717586910532</v>
+        <v>0.0002278035042605569</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002651547206002469</v>
+        <v>7.497111845463089e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0003042405144451477</v>
+        <v>-0.0004707941290448686</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003331269724504455</v>
+        <v>0.000565976343563679</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0006103419260101827</v>
+        <v>0.0001623593706180759</v>
       </c>
       <c r="EL8" t="n">
-        <v>2.844141069397177e-05</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001341738060411934</v>
+        <v>0.0002228354780345803</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0005669576018178052</v>
+        <v>0.0001237264609424915</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0002580737525806981</v>
+        <v>0.000333461532629864</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-6.659782489353283e-05</v>
+        <v>2.118308792112278e-06</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>-8.771929824560876e-06</v>
       </c>
       <c r="ET8" t="n">
-        <v>-1.825483753195301e-05</v>
+        <v>0.0005102043065939004</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0004282030696949601</v>
+        <v>-9.571209800915414e-06</v>
       </c>
       <c r="EV8" t="n">
-        <v>9.567807119190419e-05</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0002663043903360363</v>
+        <v>0.0001148545176110349</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0003019874716394505</v>
+        <v>0.000529324369285103</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0003013253132542165</v>
+        <v>-1.816607318283757e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002815829528158298</v>
+        <v>0.002094440213252125</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003543859649122883</v>
+        <v>0.002703746620316682</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004929844520287884</v>
+        <v>0.002530612244897912</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003445635528330993</v>
+        <v>0.001407914764079199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001066260472201019</v>
+        <v>0.0007667031763417764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002350877192982514</v>
+        <v>0.001877551020408152</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001761102603369058</v>
+        <v>0.002912280701754344</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003579588728103556</v>
+        <v>0.003120243531202471</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004596369254538435</v>
+        <v>0.008767864040169904</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0005263157894737525</v>
+        <v>0.002207001522070073</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000455062571103515</v>
+        <v>0.002471996910003815</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002081051478641871</v>
+        <v>0.0008748573602130217</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003292496171516091</v>
+        <v>0.004071537290715421</v>
       </c>
       <c r="O9" t="n">
-        <v>0.006947368421052669</v>
+        <v>0.004185692541856967</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001017543859649161</v>
+        <v>0.002624572080639098</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02332947083816144</v>
+        <v>0.02062572421784469</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001649122807017589</v>
+        <v>0.001715954728002922</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003995433789954328</v>
+        <v>0.003564656806977639</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0007667031763417653</v>
+        <v>0.00216812476226711</v>
       </c>
       <c r="U9" t="n">
-        <v>0.005824561403508832</v>
+        <v>0.003476245654692889</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001614035087719357</v>
+        <v>0.00993150684931512</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001877551020408186</v>
+        <v>0.001820250284414138</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004260174971471997</v>
+        <v>0.003306122448979521</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00231749710312863</v>
+        <v>0.004210119737350282</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0111239860950174</v>
+        <v>0.02499034376207025</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004414003044140025</v>
+        <v>0.02149106124001525</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006085964244959996</v>
+        <v>0.00128934395146002</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.002220520673813164</v>
+        <v>0.00389473684210524</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02699884125144846</v>
+        <v>0.01093086133642327</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01438481197517344</v>
+        <v>0.01022270901788974</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003431909456005855</v>
+        <v>0.006164383561643882</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001438596491228128</v>
+        <v>0.004854000758437638</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001510204081632671</v>
+        <v>0.001521491061240055</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.002578687902919952</v>
+        <v>0.001782328403488842</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.006666666666666698</v>
+        <v>0.008981380065717437</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01345801246791342</v>
+        <v>0.019544225569718</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001931247585940532</v>
+        <v>0.001255707762557123</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01224800304298209</v>
+        <v>0.01510079878280721</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002450229709035234</v>
+        <v>0.01637697952877557</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.004350877192982527</v>
+        <v>0.005228070175438559</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001148545176110283</v>
+        <v>0.002054012932674099</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.005732018985031051</v>
+        <v>0.01004248744689063</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01201168309602044</v>
+        <v>0.02347572106608253</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.002974121282348407</v>
+        <v>0.001978691019786949</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0007616146230007281</v>
+        <v>0.0003427265803503499</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002736842105263204</v>
+        <v>0.007338740826573919</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003052631578947429</v>
+        <v>0.003082191780821963</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001423877327491807</v>
+        <v>0.001058780576852891</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002750275027502702</v>
+        <v>0.0007616146230007504</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.002566923359002515</v>
+        <v>0.008420239474700598</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.003795918367346984</v>
+        <v>0.01308771929824557</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.02614035087719304</v>
+        <v>0.02326315789473681</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01919660100424878</v>
+        <v>0.02442105263157893</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001180502665651129</v>
+        <v>0.001940639269406463</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001521491061239999</v>
+        <v>0.0009893455098934911</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.009647779479326202</v>
+        <v>0.00681645087585685</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.02217543859649129</v>
+        <v>0.01677192982456139</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0188771929824562</v>
+        <v>0.01831578947368418</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0004950495049504733</v>
+        <v>0.0007719298245613682</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.01904210119737353</v>
+        <v>0.01601369341955121</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.005870992661259167</v>
+        <v>0.008613364233294674</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.000880088008800839</v>
+        <v>0.003046458492003079</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001052631578947427</v>
+        <v>0.001407914764079199</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001023890784982884</v>
+        <v>0.002283105022831078</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02438596491228075</v>
+        <v>0.01884210526315788</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.003922315308453894</v>
+        <v>0.0023947470065662</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001370906321401333</v>
+        <v>0.001483453784709066</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.006280701754386031</v>
+        <v>0.00550877192982453</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0006067500948046644</v>
+        <v>0.001217656012176616</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005122807017543918</v>
+        <v>0.001137656427758871</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001066260472201019</v>
+        <v>0.003652968036529714</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002246763137852226</v>
+        <v>0.001017543859649095</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.50877192982546e-05</v>
+        <v>0.0003673469387755146</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001787751996956999</v>
+        <v>0.003669370413286932</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003522205206738149</v>
+        <v>0.002858246427191913</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004198612632347587</v>
+        <v>0.006421052631578906</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001508771929824604</v>
+        <v>0.001706484641638262</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003929824561403561</v>
+        <v>0.006245614035087688</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.001540154015401496</v>
+        <v>0.008420239474700608</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.005832367709540365</v>
+        <v>0.002510460251046098</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.006912280701754436</v>
+        <v>0.002473363774733684</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.002450229709035223</v>
+        <v>0.004480494399381951</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0005133846718004653</v>
+        <v>0.001826484018264896</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001789794364051744</v>
+        <v>0.005832367709540298</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0008067473414007708</v>
+        <v>0.0003046458492002912</v>
       </c>
       <c r="CJ9" t="n">
-        <v>7.334066740005696e-05</v>
+        <v>0.0001516875237011828</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001942117288651901</v>
+        <v>0.00209205020920511</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.006105263157894792</v>
+        <v>0.005407493240633399</v>
       </c>
       <c r="CM9" t="n">
+        <v>0.0007656967840735329</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0004746257758306171</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.001597565614302032</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0004977029096478014</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.002067381316998484</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.001674277016742831</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.001978691019786971</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0004564473183720219</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0006825938566553224</v>
+      </c>
+      <c r="CV9" t="n">
         <v>0.0008039816232772168</v>
       </c>
-      <c r="CN9" t="n">
-        <v>0.002526799387442569</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.001102040816326544</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0.0001522070015220756</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>0.003461392164320998</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.001544998068752434</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0.002786945361202731</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0.001904036557501854</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0.0003508771929825017</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0.00136842105263163</v>
-      </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002530253025302476</v>
+        <v>0.00137825421133233</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.001684532924961713</v>
+        <v>0.001179604261796108</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0002920774005111371</v>
+        <v>0.002356122054847387</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0005705591479649996</v>
+        <v>0.0003805175038051889</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001531393568147021</v>
+        <v>0.001408987052551447</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001028179741050994</v>
+        <v>0.001197373503283072</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0003157894736842915</v>
+        <v>0.0006233956729005729</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.001614035087719334</v>
+        <v>0.002411944869831561</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.001607963246554356</v>
+        <v>0.00232115677321163</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001789473684210574</v>
+        <v>0.0004188880426504005</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002285714285714313</v>
+        <v>0.001102040816326533</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001186830015313933</v>
+        <v>0.004905368868288851</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001387367652427896</v>
+        <v>0.000550055005500516</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0006952491309386022</v>
+        <v>0.0008163265306122547</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002807017543860147</v>
+        <v>0.000957120980091919</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0024912280701755</v>
+        <v>0.001749714720426077</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.004612244897959239</v>
+        <v>0.0005841548010222852</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.002123625331816426</v>
+        <v>0.00326530612244893</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0006067500948046756</v>
+        <v>0.002161547212741777</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.000949251551661201</v>
+        <v>0.0009859689040576879</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0005133846718004653</v>
+        <v>0.0007205157375806181</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0008722032612817233</v>
+        <v>0.000386249517188042</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0009188361408882017</v>
+        <v>0.0008342813803564941</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001241328952172338</v>
+        <v>0.008188489764387741</v>
       </c>
       <c r="DV9" t="n">
-        <v>7.724990343762616e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0004977029096477792</v>
+        <v>0.000492984452028844</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.00253061224489799</v>
+        <v>0.002896871378910726</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.000455062571103515</v>
+        <v>0.002612244897959149</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004897959183673528</v>
+        <v>0.0002857142857142892</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.003265306122449019</v>
+        <v>0.00142912321359594</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001503483681701467</v>
+        <v>0.000474625775830606</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001387755102040833</v>
+        <v>0.001569678407350694</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0007346938775510293</v>
+        <v>0.0002555677254472366</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0004211332312404337</v>
+        <v>0.0005306122448979656</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0006466337010269996</v>
+        <v>0.0006938775510204164</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0006854531607006553</v>
+        <v>0.0009889691898060215</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0007301935012778759</v>
+        <v>0.0006206644760861968</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.006315789473684263</v>
+        <v>0.0002284843869002184</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0008497489378138323</v>
+        <v>0.001622247972190005</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001225114854517628</v>
+        <v>0.001204819277108449</v>
       </c>
       <c r="EL9" t="n">
-        <v>3.80807311500364e-05</v>
+        <v>7.610350076105998e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003808073115003641</v>
+        <v>0.0009795918367347055</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.00148514851485142</v>
+        <v>0.000350877192982435</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.001142857142857157</v>
+        <v>0.00072298325722987</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001224489795918382</v>
+        <v>0.0003046458492002912</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>0.0009893455098934911</v>
       </c>
       <c r="ES9" t="n">
-        <v>0</v>
+        <v>3.828483920367276e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001020408163265318</v>
+        <v>0.001368421052631585</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002713604693802663</v>
+        <v>0.00121350018960944</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0007996953541507645</v>
+        <v>0.000386249517188042</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0008771929824561986</v>
+        <v>0.00210526315789471</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.002053538687202006</v>
+        <v>0.002367346938775483</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001298245614035121</v>
+        <v>0.0007987828071510216</v>
       </c>
     </row>
   </sheetData>
